--- a/Data/Exports/Report.xlsx
+++ b/Data/Exports/Report.xlsx
@@ -1,43 +1,82 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x15">
-  <x:fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <x:workbookPr codeName="ThisWorkbook" defaultThemeVersion="164011"/>
+<x:workbook xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <x:fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <x:workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ChaitanyaRavindra\Documents\UiPath\ConocoPhillips-Performer\Data\Exports\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3306A2B8-312F-4607-924C-F3921A3610C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" firstSheet="0" activeTab="0"/>
+    <x:workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="0" activeTab="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <x:sheet name="Report" sheetId="2" r:id="rId1"/>
   </x:sheets>
   <x:definedNames/>
-  <x:calcPr calcId="162913"/>
-  <x:extLst>
-    <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </x:ext>
-  </x:extLst>
+  <x:calcPr calcId="0"/>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:si>
+    <x:t>ReferenceID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FilePath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PageNo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Status</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Reason</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03 2023 ETC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\05 EnergyTransfer-ETC-EagleFord\03 2023 ETC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Success</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03 2023 Thompsonville Statement.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\06 Enterprise-EPCO-EagleFord\03 2023 Thompsonville Statement.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03 2023 Yoakum Plant Stmt.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\06 Enterprise-EPCO-EagleFord\03 2023 Yoakum Plant Stmt.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04 2023 DCP Stmt.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\04 DCP-DCP-Eagleford\04 2023 DCP Stmt.pdf</x:t>
+  </x:si>
+</x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<x:styleSheet xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac x16r2">
+<x:styleSheet xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac x16r2 xr">
   <x:numFmts count="1">
     <x:numFmt numFmtId="0" formatCode=""/>
   </x:numFmts>
-  <x:fonts count="2" x14ac:knownFonts="1">
+  <x:fonts count="1" x14ac:knownFonts="1">
     <x:font>
-      <x:sz val="11"/>
-      <x:color theme="1"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
@@ -62,7 +101,7 @@
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
   </x:cellStyleXfs>
   <x:cellXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -93,44 +132,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -157,15 +196,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -192,7 +230,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -204,155 +241,260 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{00000000-0001-0000-0000-000000000000}" mc:Ignorable="x14ac xr xr2 xr3">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1"/>
+  <x:dimension ref="A1:E4"/>
   <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <x:sheetData/>
+  <x:cols>
+    <x:col min="1" max="1" width="20.285156" style="0" bestFit="1" customWidth="1"/>
+    <x:col min="2" max="2" width="139.710938" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="7.855469" style="0" bestFit="1" customWidth="1"/>
+    <x:col min="4" max="4" width="7.710938" style="0" bestFit="1" customWidth="1"/>
+    <x:col min="5" max="5" width="7.425781" style="0" bestFit="1" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A1" s="0" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B1" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C1" s="0" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D1" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E1" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A2" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A3" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A4" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:5">
+      <x:c r="A5" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
   <x:tableParts count="0"/>

--- a/Data/Exports/Report.xlsx
+++ b/Data/Exports/Report.xlsx
@@ -66,6 +66,12 @@
   </x:si>
   <x:si>
     <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\04 DCP-DCP-Eagleford\04 2023 DCP Stmt.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12 2022 KMC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\03 Copano-KM-EagleFord\12 2022 KMC Stmts.pdf</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -492,6 +498,17 @@
         <x:v>8</x:v>
       </x:c>
     </x:row>
+    <x:row r="6" spans="1:5">
+      <x:c r="A6" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/Data/Exports/Report.xlsx
+++ b/Data/Exports/Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ChaitanyaRavindra\Documents\UiPath\ConocoPhillips-Performer\Data\Exports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3306A2B8-312F-4607-924C-F3921A3610C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{983A7BD3-8448-4BB5-92FB-66189A2F6A7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <x:bookViews>
     <x:workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="0" activeTab="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </x:bookViews>
@@ -38,16 +38,97 @@
     <x:t>Reason</x:t>
   </x:si>
   <x:si>
+    <x:t>01 2023 DCP Stmt.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\04 DCP-DCP-Eagleford\01 2023 DCP Stmt.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Success</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01 2023 KMC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\03 Copano-KM-EagleFord\01 2023 KMC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01 2023 ETC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\05 EnergyTransfer-ETC-EagleFord\01 2023 ETC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02 2023 DCP Stmt.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\04 DCP-DCP-Eagleford\02 2023 DCP Stmt.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02 2023 KMC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\03 Copano-KM-EagleFord\02 2023 KMC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03 2023 DCP Stmt.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\04 DCP-DCP-Eagleford\03 2023 DCP Stmt.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04 2023 DCP Stmt.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\04 DCP-DCP-Eagleford\04 2023 DCP Stmt.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05 2023 DCP Stmt.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\04 DCP-DCP-Eagleford\05 2023 DCP Stmt.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01 2023 Thompsonville Statement.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\06 Enterprise-EPCO-EagleFord\01 2023 Thompsonville Statement.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01 2023 Yoakum Plant Stmt.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\06 Enterprise-EPCO-EagleFord\01 2023 Yoakum Plant Stmt.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02 2023 ETC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\05 EnergyTransfer-ETC-EagleFord\02 2023 ETC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02 2023 Thompsonville Statement.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\06 Enterprise-EPCO-EagleFord\02 2023 Thompsonville Statement.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02 2023 Yoakum Plant Stmt.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\06 Enterprise-EPCO-EagleFord\02 2023 Yoakum Plant Stmt.pdf</x:t>
+  </x:si>
+  <x:si>
     <x:t>03 2023 ETC Stmts.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\05 EnergyTransfer-ETC-EagleFord\03 2023 ETC Stmts.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>Success</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-</x:t>
+    <x:t>03 2023 KMC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\03 Copano-KM-EagleFord\03 2023 KMC Stmts.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>03 2023 Thompsonville Statement.pdf</x:t>
@@ -62,16 +143,703 @@
     <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\06 Enterprise-EPCO-EagleFord\03 2023 Yoakum Plant Stmt.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>04 2023 DCP Stmt.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\04 DCP-DCP-Eagleford\04 2023 DCP Stmt.pdf</x:t>
+    <x:t>04 2023 ETC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\05 EnergyTransfer-ETC-EagleFord\04 2023 ETC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04 2023 KMC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\03 Copano-KM-EagleFord\04 2023 KMC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04 2023 Thompsonville Statement.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\06 Enterprise-EPCO-EagleFord\04 2023 Thompsonville Statement.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04 2023 Yoakum Plant Stmt.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\06 Enterprise-EPCO-EagleFord\04 2023 Yoakum Plant Stmt.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06 2023 DCP Stmt.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\04 DCP-DCP-Eagleford\06 2023 DCP Stmt.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06 2023 ETC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\05 EnergyTransfer-ETC-EagleFord\06 2023 ETC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06 2023 KMC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\03 Copano-KM-EagleFord\06 2023 KMC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07 2023 DCP Stmt.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\04 DCP-DCP-Eagleford\07 2023 DCP Stmt.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07 2023 ETC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\05 EnergyTransfer-ETC-EagleFord\07 2023 ETC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07 2023 KMC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\03 Copano-KM-EagleFord\07 2023 KMC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08 2022 DCP Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\04 DCP-DCP-Eagleford\08 2022 DCP Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08 2022 KMC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\03 Copano-KM-EagleFord\08 2022 KMC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09 2022 DCP Statements.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\04 DCP-DCP-Eagleford\09 2022 DCP Statements.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09 2022 KMC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\03 Copano-KM-EagleFord\09 2022 KMC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10 2022 DCP Statements.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\04 DCP-DCP-Eagleford\10 2022 DCP Statements.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10 2022 KMC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\03 Copano-KM-EagleFord\10 2022 KMC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11 2022 DCP Stmt.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\04 DCP-DCP-Eagleford\11 2022 DCP Stmt.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11 2022 KMC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\03 Copano-KM-EagleFord\11 2022 KMC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12 2022 DCP Stmt.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\04 DCP-DCP-Eagleford\12 2022 DCP Stmt.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>12 2022 KMC Stmts.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\03 Copano-KM-EagleFord\12 2022 KMC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05 2023 ETC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\05 EnergyTransfer-ETC-EagleFord\05 2023 ETC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05 2023 KMC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\03 Copano-KM-EagleFord\05 2023 KMC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05 2023 Thompsonville Statement.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\06 Enterprise-EPCO-EagleFord\05 2023 Thompsonville Statement.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05 2023 Yoakum Plant Stmt.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\06 Enterprise-EPCO-EagleFord\05 2023 Yoakum Plant Stmt.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06 2023 Thompsonville Statement.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\06 Enterprise-EPCO-EagleFord\06 2023 Thompsonville Statement.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06 2023 Yoakum Plant Stmt.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\06 Enterprise-EPCO-EagleFord\06 2023 Yoakum Plant Stmt.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07 2023 Thompsonville Statement.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\06 Enterprise-EPCO-EagleFord\07 2023 Thompsonville Statement.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07 2023 Yoakum Plant Stmt.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\06 Enterprise-EPCO-EagleFord\07 2023 Yoakum Plant Stmt.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08 2022 ETC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\05 EnergyTransfer-ETC-EagleFord\08 2022 ETC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08 2022 Thompsonville Statement.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\06 Enterprise-EPCO-EagleFord\08 2022 Thompsonville Statement.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08 2022 Yoakum Plant Stmt.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\06 Enterprise-EPCO-EagleFord\08 2022 Yoakum Plant Stmt.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09 2022 ETC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\05 EnergyTransfer-ETC-EagleFord\09 2022 ETC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09 2022 Thompsonville Statement.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\06 Enterprise-EPCO-EagleFord\09 2022 Thompsonville Statement.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09 2022 Yoakum Plant Stmt.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\06 Enterprise-EPCO-EagleFord\09 2022 Yoakum Plant Stmt.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10 2022 ETC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\05 EnergyTransfer-ETC-EagleFord\10 2022 ETC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10 2022 Thompsonville Statement.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\06 Enterprise-EPCO-EagleFord\10 2022 Thompsonville Statement.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10 2022 Yoakum Plant Stmt.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\06 Enterprise-EPCO-EagleFord\10 2022 Yoakum Plant Stmt.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11 2022 ETC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\05 EnergyTransfer-ETC-EagleFord\11 2022 ETC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11 2022 Thompsonville Statement.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\06 Enterprise-EPCO-EagleFord\11 2022 Thompsonville Statement.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11 2022 Yoakum Plant Stmt.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\06 Enterprise-EPCO-EagleFord\11 2022 Yoakum Plant Stmt.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1102775_GAS_STMT_H_1.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\01 Hiland-Hiland-Bakken\1102775_GAS_STMT_H_1.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1108695_GAS_STMT_H_1.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\01 Hiland-Hiland-Bakken\1108695_GAS_STMT_H_1.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1115602_GAS_STMT_H_1.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\01 Hiland-Hiland-Bakken\1115602_GAS_STMT_H_1.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The process cannot access the file 'C:\Users\ChaitanyaRavindra\Documents\UiPath\ConocoPhillips-Performer\Data\Exports\Output.xlsx' because it is being used by another process.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1121920_GAS_STMT_H_1.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\01 Hiland-Hiland-Bakken\1121920_GAS_STMT_H_1.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1127369_GAS_STMT_H_1.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\01 Hiland-Hiland-Bakken\1127369_GAS_STMT_H_1.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1133769_GAS_STMT_H_1.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\01 Hiland-Hiland-Bakken\1133769_GAS_STMT_H_1.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1138700_GAS_STMT_H_1.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\01 Hiland-Hiland-Bakken\1138700_GAS_STMT_H_1.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1156085_GAS_STMT_H_1.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\01 Hiland-Hiland-Bakken\1156085_GAS_STMT_H_1.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1161790_GAS_STMT_H_1.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\01 Hiland-Hiland-Bakken\1161790_GAS_STMT_H_1.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1167928_GAS_STMT_H_1.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\01 Hiland-Hiland-Bakken\1167928_GAS_STMT_H_1.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1174191_GAS_STMT_H_1.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\01 Hiland-Hiland-Bakken\1174191_GAS_STMT_H_1.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1178524_GAS_STMT_H_1.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\01 Hiland-Hiland-Bakken\1178524_GAS_STMT_H_1.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12 2022 ETC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\05 EnergyTransfer-ETC-EagleFord\12 2022 ETC Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12 2022 Thompsonville Statement.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\06 Enterprise-EPCO-EagleFord\12 2022 Thompsonville Statement.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12 2022 Yoakum Plant Stmt.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\06 Enterprise-EPCO-EagleFord\12 2022 Yoakum Plant Stmt.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Enterprise - Carlsbad - Permian.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\07 Enterprise-Carlsbad-Permian\Enterprise - Carlsbad - Permian.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2012 RSP- Loving Plant Gas Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\09 Targa-LovingPlant-Permian\2012 RSP- Loving Plant Gas Stmts.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>78-78</x:t>
+  </x:si>
+  <x:si>
+    <x:t>40-40</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Permian Statement Targa - Carlsbad 052023_10.55.51.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\08 Targa-Carlsbad-Permian\Permian Statement Targa - Carlsbad 052023_10.55.51.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3-3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38-38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SS_999_10013461_01-01-2023_02-28-2023.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\15 WTG-SouthBenedum-Permian\SS_999_10013461_01-01-2023_02-28-2023.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SS_999_10013461_02-01-2023_03-28-2023.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\15 WTG-SouthBenedum-Permian\SS_999_10013461_02-01-2023_03-28-2023.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SS_999_10013461_03-01-2023_04-27-2023.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\15 WTG-SouthBenedum-Permian\SS_999_10013461_03-01-2023_04-27-2023.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SS_999_10013461_04-01-2023_05-26-2023.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\15 WTG-SouthBenedum-Permian\SS_999_10013461_04-01-2023_05-26-2023.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2-2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Failed opening the Excel file C:\Users\ChaitanyaRavindra\Documents\UiPath\ConocoPhillips-Performer\Data\Exports\Output.xlsx. Possible reasons: the file is corrupt, the file is already used by another process, you don't have permissions to open the file or the file has incorrect sensitivity label. </x:t>
+  </x:si>
+  <x:si>
+    <x:t>SS_999_10013461_05-01-2023_06-28-2023.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\15 WTG-SouthBenedum-Permian\SS_999_10013461_05-01-2023_06-28-2023.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5-5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SS_999_10013461_06-01-2023_07-27-2023.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\15 WTG-SouthBenedum-Permian\SS_999_10013461_06-01-2023_07-27-2023.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4-4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SS_999_10013461_07-01-2023_08-28-2023.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\15 WTG-SouthBenedum-Permian\SS_999_10013461_07-01-2023_08-28-2023.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SS_999_10156711_01-01-2023_02-28-2023.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\14 WTG-SaleRanch-Permian\SS_999_10156711_01-01-2023_02-28-2023.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SS_999_10156711_02-01-2023_03-28-2023.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\14 WTG-SaleRanch-Permian\SS_999_10156711_02-01-2023_03-28-2023.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SS_999_10156711_03-01-2023_04-27-2023.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\14 WTG-SaleRanch-Permian\SS_999_10156711_03-01-2023_04-27-2023.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SS_999_10156711_04-01-2023_05-26-2023.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\14 WTG-SaleRanch-Permian\SS_999_10156711_04-01-2023_05-26-2023.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SS_999_10156711_05-01-2023_06-28-2023.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\14 WTG-SaleRanch-Permian\SS_999_10156711_05-01-2023_06-28-2023.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SS_999_10156711_06-01-2023_07-27-2023.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\14 WTG-SaleRanch-Permian\SS_999_10156711_06-01-2023_07-27-2023.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SS_999_10156711_07-01-2023_08-28-2023.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\14 WTG-SaleRanch-Permian\SS_999_10156711_07-01-2023_08-28-2023.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13-13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Targa - Loving Plant - Permian.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\09 Targa-LovingPlant-Permian\Targa - Loving Plant - Permian.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WFSS_118_20230101_20230101_32337.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\12 Targa-SouthLea-Permian\WFSS_118_20230101_20230101_32337.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>104-104</x:t>
+  </x:si>
+  <x:si>
+    <x:t>60-60</x:t>
+  </x:si>
+  <x:si>
+    <x:t>140-140</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70-70</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WFSS_118_20230201_20230201_32337.PDF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\12 Targa-SouthLea-Permian\WFSS_118_20230201_20230201_32337.PDF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15-15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14-14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27-27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WFSS_118_20230301_20230301_32337.PDF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\12 Targa-SouthLea-Permian\WFSS_118_20230301_20230301_32337.PDF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22-22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20-20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>155-155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WFSS_118_20230401_20230401_32337.PDF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\12 Targa-SouthLea-Permian\WFSS_118_20230401_20230401_32337.PDF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>92-92</x:t>
+  </x:si>
+  <x:si>
+    <x:t>143-143</x:t>
+  </x:si>
+  <x:si>
+    <x:t>41-41</x:t>
+  </x:si>
+  <x:si>
+    <x:t>112-112</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WFSS_118_20230501_20230501_32337.PDF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\12 Targa-SouthLea-Permian\WFSS_118_20230501_20230501_32337.PDF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>122-122</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30-30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>81-81</x:t>
+  </x:si>
+  <x:si>
+    <x:t>154-154</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WFSS_118_20230601_20230601_32337.PDF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\12 Targa-SouthLea-Permian\WFSS_118_20230601_20230601_32337.PDF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>139-139</x:t>
+  </x:si>
+  <x:si>
+    <x:t>67-67</x:t>
+  </x:si>
+  <x:si>
+    <x:t>33-33</x:t>
+  </x:si>
+  <x:si>
+    <x:t>158-158</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WFSS_118_20230701_20230701_32337.PDF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\12 Targa-SouthLea-Permian\WFSS_118_20230701_20230701_32337.PDF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>159-159</x:t>
+  </x:si>
+  <x:si>
+    <x:t>111-111</x:t>
+  </x:si>
+  <x:si>
+    <x:t>58-58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>132-132</x:t>
+  </x:si>
+  <x:si>
+    <x:t>62-62</x:t>
+  </x:si>
+  <x:si>
+    <x:t>91-91</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BlobFileInfo does not exist.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WFSS_142_20230101_20230101_32306.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\13 Targa-WestTexas-Permian\WFSS_142_20230101_20230101_32306.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16-16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WFSS_142_20230101_20230101_32337.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\13 Targa-WestTexas-Permian\WFSS_142_20230101_20230101_32337.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>102-102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>32-32</x:t>
+  </x:si>
+  <x:si>
+    <x:t>89-89</x:t>
+  </x:si>
+  <x:si>
+    <x:t>142-142</x:t>
+  </x:si>
+  <x:si>
+    <x:t>144-144</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WFSS_293_20230501_20230501_32337.PDF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\11 Targa-SandHills-Permian\WFSS_293_20230501_20230501_32337.PDF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WFSS_293_20230501_20230501_41038.PDF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\10 Targa-Midstream-Permian\WFSS_293_20230501_20230501_41038.PDF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WFSS_293_20230601_20230601_32337.PDF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\11 Targa-SandHills-Permian\WFSS_293_20230601_20230601_32337.PDF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WFSS_293_20230601_20230601_41038.PDF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\10 Targa-Midstream-Permian\WFSS_293_20230601_20230601_41038.PDF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WFSS_293_20230701_20230701_32337.PDF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\11 Targa-SandHills-Permian\WFSS_293_20230701_20230701_32337.PDF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8-8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WFSS_293_20230701_20230701_41038.PDF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\10 Targa-Midstream-Permian\WFSS_293_20230701_20230701_41038.PDF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OneOK - OneOK - Bakken (part 2).pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\Users\ChaitanyaRavindra\Documents\UiPath\Dispatcher-ConocoPhillips\Data\Inputs\02 OneOK-OneOK-Bakken\OneOK - OneOK - Bakken (part 2).pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>115-115</x:t>
+  </x:si>
+  <x:si>
+    <x:t>96-96</x:t>
+  </x:si>
+  <x:si>
+    <x:t>121-121</x:t>
+  </x:si>
+  <x:si>
+    <x:t>200-200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43-43</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1-1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7-7</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -415,14 +1183,14 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E4"/>
+  <x:dimension ref="A1:E112"/>
   <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <x:cols>
-    <x:col min="1" max="1" width="20.285156" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="2" max="2" width="139.710938" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="52" style="0" bestFit="1" customWidth="1"/>
+    <x:col min="2" max="2" width="158.710938" style="0" bestFit="1" customWidth="1"/>
     <x:col min="3" max="3" width="7.855469" style="0" bestFit="1" customWidth="1"/>
     <x:col min="4" max="4" width="7.710938" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="5" max="5" width="7.425781" style="0" bestFit="1" customWidth="1"/>
+    <x:col min="5" max="5" width="255" style="0" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -452,60 +1220,2606 @@
       <x:c r="D2" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="E2" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
     </x:row>
     <x:row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <x:c r="A3" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>7</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <x:c r="A4" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B4" s="0" t="s">
+      <x:c r="D4" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A5" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
+      <x:c r="B5" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A6" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A7" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A8" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A9" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A10" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A11" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A12" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A13" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A14" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A15" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A16" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D16" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A17" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A18" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D18" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A19" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D19" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A20" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D20" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A21" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D21" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A22" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D22" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A23" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D23" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A24" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D24" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A25" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D25" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A26" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D26" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A27" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D27" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A28" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D28" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A29" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D29" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A30" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D30" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A31" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D31" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A32" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D32" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A33" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D33" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A34" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D34" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A35" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D35" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A36" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D36" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A37" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D37" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A38" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="D38" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A39" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D39" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A40" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D40" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A41" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D41" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A42" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D42" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A43" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D43" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A44" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D44" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A45" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D45" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A46" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D46" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A47" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D47" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A48" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D48" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A49" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D49" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A50" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="D50" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A51" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="D51" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A52" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D52" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A53" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="D53" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A54" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="D54" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A55" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="B55" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="D55" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A56" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="B56" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="D56" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A57" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="B57" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D57" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A58" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="B58" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="D58" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A59" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B59" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="D59" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A60" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="B60" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="D60" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A61" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="B61" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="C61" s="0" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="D61" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E61" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A62" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="B62" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="D62" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A63" s="0" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="B63" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="D63" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A64" s="0" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="B64" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="D64" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A65" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="B65" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="D65" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A66" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B66" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="D66" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A67" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B67" s="0" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="D67" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A68" s="0" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="B68" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="D68" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A69" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="B69" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="D69" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A70" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="B70" s="0" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="D70" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A71" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="B71" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D71" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A72" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="B72" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D72" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A73" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="B73" s="0" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="D73" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A74" s="0" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="B74" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="D74" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A75" s="0" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="B75" s="0" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="D75" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A76" s="0" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="B76" s="0" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="C76" s="0" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="D76" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E76" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A77" s="0" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="B77" s="0" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="C77" s="0" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="D77" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E77" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A78" s="0" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="B78" s="0" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="D78" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A79" s="0" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="B79" s="0" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="C79" s="0" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="D79" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E79" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A80" s="0" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="B80" s="0" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="C80" s="0" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="D80" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E80" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A81" s="0" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="B81" s="0" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="D81" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A82" s="0" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="B82" s="0" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="D82" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A83" s="0" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="B83" s="0" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D83" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A84" s="0" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="B84" s="0" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="C84" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="D84" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E84" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A85" s="0" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="B85" s="0" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="D85" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A86" s="0" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="B86" s="0" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="C86" s="0" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="D86" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E86" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A87" s="0" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="B87" s="0" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="D87" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A88" s="0" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="B88" s="0" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="C88" s="0" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="D88" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E88" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A89" s="0" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="B89" s="0" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="D89" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A90" s="0" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="B90" s="0" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="C90" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="D90" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E90" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A91" s="0" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="B91" s="0" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="D91" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A92" s="0" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="B92" s="0" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="D92" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A93" s="0" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="B93" s="0" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="D93" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A94" s="0" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="B94" s="0" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="D94" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A95" s="0" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="B95" s="0" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="C95" s="0" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="D95" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E95" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A96" s="0" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="B96" s="0" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="D96" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A97" s="0" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="B97" s="0" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="D97" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A98" s="0" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="B98" s="0" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="D98" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A99" s="0" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="B99" s="0" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="D99" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A100" s="0" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="B100" s="0" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="C100" s="0" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="D100" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E100" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A101" s="0" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="B101" s="0" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="D101" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A102" s="0" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="B102" s="0" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="D102" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A103" s="0" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="B103" s="0" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="C103" s="0" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="D103" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E103" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A104" s="0" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="B104" s="0" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="C104" s="0" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="D104" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E104" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A105" s="0" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="B105" s="0" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="C105" s="0" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="D105" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E105" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A106" s="0" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="B106" s="0" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="C106" s="0" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="D106" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E106" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A107" s="0" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="B107" s="0" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="D107" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A108" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="B108" s="0" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="C108" s="0" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="D108" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E108" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A109" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="B109" s="0" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="C109" s="0" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="D109" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E109" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A110" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="B110" s="0" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="C110" s="0" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="D110" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E110" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A111" s="0" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="B111" s="0" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="C111" s="0" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="D111" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E111" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <x:c r="A112" s="0" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="B112" s="0" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="C112" s="0" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="D112" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E112" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" spans="1:5">
+      <x:c r="A113" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="B113" s="0" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="C113" s="0" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="D113" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E113" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" spans="1:5">
+      <x:c r="A114" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="B114" s="0" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="D114" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" spans="1:5">
+      <x:c r="A115" s="0" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="B115" s="0" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="D115" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" spans="1:5">
+      <x:c r="A116" s="0" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="B116" s="0" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="C116" s="0" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="D116" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E116" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" spans="1:5">
+      <x:c r="A117" s="0" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="B117" s="0" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="C117" s="0" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="D117" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E117" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" spans="1:5">
+      <x:c r="A118" s="0" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="B118" s="0" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="C118" s="0" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="D118" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E118" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" spans="1:5">
+      <x:c r="A119" s="0" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="B119" s="0" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="C119" s="0" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="D119" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E119" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" spans="1:5">
+      <x:c r="A120" s="0" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="B120" s="0" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="C120" s="0" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="D120" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E120" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" spans="1:5">
+      <x:c r="A121" s="0" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="B121" s="0" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="C121" s="0" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="D121" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E121" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" spans="1:5">
+      <x:c r="A122" s="0" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="B122" s="0" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="C122" s="0" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="D122" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E122" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" spans="1:5">
+      <x:c r="A123" s="0" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="B123" s="0" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="C123" s="0" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="D123" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E123" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" spans="1:5">
+      <x:c r="A124" s="0" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="B124" s="0" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="C124" s="0" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="D124" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E124" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" spans="1:5">
+      <x:c r="A125" s="0" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="B125" s="0" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="D125" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" spans="1:5">
+      <x:c r="A126" s="0" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="B126" s="0" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="C126" s="0" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="D126" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E126" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" spans="1:5">
+      <x:c r="A127" s="0" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="B127" s="0" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="C127" s="0" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="D127" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E127" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" spans="1:5">
+      <x:c r="A128" s="0" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="B128" s="0" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="C128" s="0" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="D128" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E128" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" spans="1:5">
+      <x:c r="A129" s="0" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="B129" s="0" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="C129" s="0" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="D129" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E129" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" spans="1:5">
+      <x:c r="A130" s="0" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="B130" s="0" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="D130" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" spans="1:5">
+      <x:c r="A131" s="0" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="B131" s="0" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="D131" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" spans="1:5">
+      <x:c r="A132" s="0" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="B132" s="0" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C132" s="0" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="D132" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E132" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" spans="1:5">
+      <x:c r="A133" s="0" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="B133" s="0" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C133" s="0" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="D133" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E133" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" spans="1:5">
+      <x:c r="A134" s="0" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="B134" s="0" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C134" s="0" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="D134" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E134" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" spans="1:5">
+      <x:c r="A135" s="0" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="B135" s="0" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C135" s="0" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="D135" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E135" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" spans="1:5">
+      <x:c r="A136" s="0" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="B136" s="0" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C136" s="0" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="D136" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E136" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" spans="1:5">
+      <x:c r="A137" s="0" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="B137" s="0" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C137" s="0" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="D137" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E137" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" spans="1:5">
+      <x:c r="A138" s="0" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="B138" s="0" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C138" s="0" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="D138" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E138" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" spans="1:5">
+      <x:c r="A139" s="0" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="B139" s="0" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C139" s="0" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="D139" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E139" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" spans="1:5">
+      <x:c r="A140" s="0" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="B140" s="0" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C140" s="0" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="D140" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E140" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141" spans="1:5">
+      <x:c r="A141" s="0" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="B141" s="0" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C141" s="0" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="D141" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E141" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142" spans="1:5">
+      <x:c r="A142" s="0" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="B142" s="0" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C142" s="0" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="D142" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E142" s="0" t="s">
+        <x:v>240</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143" spans="1:5">
+      <x:c r="A143" s="0" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="B143" s="0" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="C143" s="0" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="D143" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E143" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144" spans="1:5">
+      <x:c r="A144" s="0" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="B144" s="0" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="D144" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" spans="1:5">
+      <x:c r="A145" s="0" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="B145" s="0" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="C145" s="0" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="D145" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E145" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" spans="1:5">
+      <x:c r="A146" s="0" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="B146" s="0" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="C146" s="0" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="D146" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E146" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" spans="1:5">
+      <x:c r="A147" s="0" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="B147" s="0" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="C147" s="0" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="D147" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E147" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" spans="1:5">
+      <x:c r="A148" s="0" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="B148" s="0" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="C148" s="0" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="D148" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E148" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" spans="1:5">
+      <x:c r="A149" s="0" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="B149" s="0" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="C149" s="0" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="D149" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E149" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" spans="1:5">
+      <x:c r="A150" s="0" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="B150" s="0" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="C150" s="0" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D150" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E150" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" spans="1:5">
+      <x:c r="A151" s="0" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="B151" s="0" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="C151" s="0" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="D151" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E151" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" spans="1:5">
+      <x:c r="A152" s="0" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="B152" s="0" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="D152" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" spans="1:5">
+      <x:c r="A153" s="0" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="B153" s="0" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="C153" s="0" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="D153" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E153" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" spans="1:5">
+      <x:c r="A154" s="0" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="B154" s="0" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="D154" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" spans="1:5">
+      <x:c r="A155" s="0" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="B155" s="0" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="C155" s="0" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="D155" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E155" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" spans="1:5">
+      <x:c r="A156" s="0" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="B156" s="0" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="D156" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" spans="1:5">
+      <x:c r="A157" s="0" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="B157" s="0" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="D157" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" spans="1:5">
+      <x:c r="A158" s="0" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="B158" s="0" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="C158" s="0" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="D158" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E158" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" spans="1:5">
+      <x:c r="A159" s="0" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="B159" s="0" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="D159" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" spans="1:5">
+      <x:c r="A160" s="0" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="B160" s="0" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="C160" s="0" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="D160" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E160" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" spans="1:5">
+      <x:c r="A161" s="0" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="B161" s="0" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="D161" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" spans="1:5">
+      <x:c r="A162" s="0" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="B162" s="0" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="C162" s="0" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="D162" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E162" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163" spans="1:5">
+      <x:c r="A163" s="0" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="B163" s="0" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="C163" s="0" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="D163" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E163" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" spans="1:5">
+      <x:c r="A164" s="0" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="B164" s="0" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="C164" s="0" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="D164" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E164" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165" spans="1:5">
+      <x:c r="A165" s="0" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="B165" s="0" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="C165" s="0" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="D165" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E165" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" spans="1:5">
+      <x:c r="A166" s="0" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="B166" s="0" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="C166" s="0" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="D166" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E166" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" spans="1:5">
+      <x:c r="A167" s="0" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="B167" s="0" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="C167" s="0" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="D167" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E167" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168" spans="1:5">
+      <x:c r="A168" s="0" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="B168" s="0" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="D168" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" spans="1:5">
+      <x:c r="A169" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B169" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C169" s="0" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="D169" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E169" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" spans="1:5">
+      <x:c r="A170" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B170" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D170" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171" spans="1:5">
+      <x:c r="A171" s="0" t="s">
         <x:v>8</x:v>
       </x:c>
-    </x:row>
-    <x:row r="5" spans="1:5">
-      <x:c r="A5" s="0" t="s">
+      <x:c r="B171" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D171" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172" spans="1:5">
+      <x:c r="A172" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B172" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B5" s="0" t="s">
+      <x:c r="C172" s="0" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="D172" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E172" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173" spans="1:5">
+      <x:c r="A173" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B173" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D173" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174" spans="1:5">
+      <x:c r="A174" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:5">
-      <x:c r="A6" s="0" t="s">
+      <x:c r="B174" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B6" s="0" t="s">
+      <x:c r="C174" s="0" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="D174" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E174" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175" spans="1:5">
+      <x:c r="A175" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B175" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C175" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="D175" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E175" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176" spans="1:5">
+      <x:c r="A176" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B176" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D176" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177" spans="1:5">
+      <x:c r="A177" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D6" s="0" t="s">
+      <x:c r="B177" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C177" s="0" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="D177" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E177" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178" spans="1:5">
+      <x:c r="A178" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B178" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D178" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179" spans="1:5">
+      <x:c r="A179" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B179" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C179" s="0" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="D179" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E179" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180" spans="1:5">
+      <x:c r="A180" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B180" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D180" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181" spans="1:5">
+      <x:c r="A181" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B181" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C181" s="0" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="D181" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E181" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182" spans="1:5">
+      <x:c r="A182" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B182" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C182" s="0" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="D182" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E182" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183" spans="1:5">
+      <x:c r="A183" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B183" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C183" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="D183" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E183" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184" spans="1:5">
+      <x:c r="A184" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B184" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D184" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185" spans="1:5">
+      <x:c r="A185" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B185" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="C185" s="0" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="D185" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E185" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186" spans="1:5">
+      <x:c r="A186" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B186" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C186" s="0" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="D186" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E186" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187" spans="1:5">
+      <x:c r="A187" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B187" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D187" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188" spans="1:5">
+      <x:c r="A188" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B188" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C188" s="0" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="D188" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E188" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189" spans="1:5">
+      <x:c r="A189" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B189" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D189" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190" spans="1:5">
+      <x:c r="A190" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B190" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C190" s="0" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="D190" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E190" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191" spans="1:5">
+      <x:c r="A191" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B191" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D191" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192" spans="1:5">
+      <x:c r="A192" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B192" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C192" s="0" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="D192" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E192" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193" spans="1:5">
+      <x:c r="A193" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B193" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D193" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194" spans="1:5">
+      <x:c r="A194" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B194" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C194" s="0" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="D194" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E194" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195" spans="1:5">
+      <x:c r="A195" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B195" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D195" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196" spans="1:5">
+      <x:c r="A196" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B196" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D196" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
     </x:row>
